--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574580041</v>
+        <v>46157.93118394383</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118394383</v>
+        <v>46157.93183825448</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183825448</v>
+        <v>46157.9340588478</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9340588478</v>
+        <v>46157.93723968606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723968606</v>
+        <v>46158.28221758628</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221758628</v>
+        <v>46158.29702565955</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702565955</v>
+        <v>46158.29821529606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821529606</v>
+        <v>46158.33392746468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392746468</v>
+        <v>46158.36862533476</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862533476</v>
+        <v>46158.37293494685</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
